--- a/step3-validation-check.xlsx
+++ b/step3-validation-check.xlsx
@@ -454,13 +454,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3094,86 +3094,86 @@
       <c r="H69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>同意事項</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>両方未チェック時</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>次画面ボタン非アクティブ</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>disabled</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>Step3のボタン制御なし</t>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>updateBtn() agreeチェック判定</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>両方チェック必須に</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>全体</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Step3エラー制御</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>エラー時ボタン非アクティブ</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>checkStep3Errors相当</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>Step3版のcheckErrors未実装</t>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>updateBtn() step3Content内.error.show検知</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Step別updateBtn実装</t>
         </is>
       </c>
     </row>

--- a/step3-validation-check.xlsx
+++ b/step3-validation-check.xlsx
@@ -2862,44 +2862,44 @@
       <c r="H63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>適格性質問</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>質問⑨</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Yes時詳細入力</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>渡航日/目的/期間の入力欄</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>未実装</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>Yes回答時のサブ質問なし</t>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>省略（「はい」回答時はESTA認証不可のためサブ質問不要）</t>
         </is>
       </c>
     </row>
